--- a/output/pdf_financials_xlsx/CCO.xlsx
+++ b/output/pdf_financials_xlsx/CCO.xlsx
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.236132</v>
+        <v>0.07023699999999999</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.238893</v>
+        <v>0.09241099999999999</v>
       </c>
     </row>
     <row r="12">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.005774</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.001792</v>
       </c>
     </row>
     <row r="41">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.40235</v>
+        <v>0.408124</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.328044</v>
+        <v>0.329836</v>
       </c>
     </row>
     <row r="42">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.110028</v>
+        <v>0.104254</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.095733</v>
+        <v>0.093941</v>
       </c>
     </row>
     <row r="49">
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="124">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="126">
@@ -3730,7 +3730,11 @@
           <t>Decrease in long-term debt</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -4324,7 +4328,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>0.07023699999999999</v>
       </c>
